--- a/docs/reviews/DBS6_Review_Rows_20260924-981b2555.xlsx
+++ b/docs/reviews/DBS6_Review_Rows_20260924-981b2555.xlsx
@@ -31186,22 +31186,22 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>deploy</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Naming only.</t>
+          <t>The name stamps BAMBOO-QUEEN-OLIVE-6PCS: 509 in FBA, 14 reserved, 2.68/day, 196 days left, but the ad serves BAMBOO-QUEEN-WHITE-6PCS: 348 in FBA, 30 reserved, 1002 inbound, 6.67/day, 57 days left, and the swap cannot load (and the swap itself is held on stock). The name would describe a child the campaign does not advertise.</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
